--- a/Config/Tables/감사한말씀_024.xlsx
+++ b/Config/Tables/감사한말씀_024.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\### 언리얼 문서 ###\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\InternationalBible\Config\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F747562E-FF3C-4E0B-9974-64F004917B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD1B0B6-221B-49C8-A7B6-A7B4E7B0DAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1880C24E-5AD4-4F93-85A2-CE7EF6D954C1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="490">
   <si>
     <t>Key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5691,6 +5691,12 @@
   </si>
   <si>
     <t>https://youtu.be/a01SOqW5x1Y</t>
+  </si>
+  <si>
+    <t>하나님을 전적으로 신뢰하면 벌어지는 5가지 기적</t>
+  </si>
+  <si>
+    <t>https://youtu.be/74yV8HeZan8</t>
   </si>
 </sst>
 </file>
@@ -6133,7 +6139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F10FF1D-7320-4AEB-83A7-7CA7576D0E25}">
-  <dimension ref="A1:D253"/>
+  <dimension ref="A1:D254"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="81.375" customWidth="1"/>
@@ -9680,6 +9686,20 @@
       </c>
       <c r="D253" t="s">
         <v>487</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>253</v>
+      </c>
+      <c r="C254" t="s">
+        <v>488</v>
+      </c>
+      <c r="D254" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Tables/감사한말씀_024.xlsx
+++ b/Config/Tables/감사한말씀_024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\InternationalBible\Config\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD1B0B6-221B-49C8-A7B6-A7B4E7B0DAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D42AF9-B269-4830-9B82-6E8A88DB655A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1880C24E-5AD4-4F93-85A2-CE7EF6D954C1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="494">
   <si>
     <t>Key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5697,6 +5697,18 @@
   </si>
   <si>
     <t>https://youtu.be/74yV8HeZan8</t>
+  </si>
+  <si>
+    <t>성경 전체 50분 총정리, 성경통독 전 필수 영상!</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vvYXNfwS_b4</t>
+  </si>
+  <si>
+    <t>창세기부터 요한계시록까지: 하나님의 구속 이야기 완전 정리</t>
+  </si>
+  <si>
+    <t>https://youtu.be/6EdxKaVuO1U</t>
   </si>
 </sst>
 </file>
@@ -6139,7 +6151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F10FF1D-7320-4AEB-83A7-7CA7576D0E25}">
-  <dimension ref="A1:D254"/>
+  <dimension ref="A1:D256"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="81.375" customWidth="1"/>
@@ -9700,6 +9712,22 @@
       </c>
       <c r="D254" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C255" t="s">
+        <v>490</v>
+      </c>
+      <c r="D255" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C256" t="s">
+        <v>492</v>
+      </c>
+      <c r="D256" t="s">
+        <v>493</v>
       </c>
     </row>
   </sheetData>
